--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonem\Documents\GitHub\void-red\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{355DD222-0A07-457F-B459-063640830EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E940B806-4F6E-48D0-9872-A752B00E7FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t>GetItem</t>
-  </si>
-  <si>
-    <t>Alv/1-2,ぬいぐるみ,よくできたぬいぐるみだ</t>
   </si>
   <si>
     <t>(エレベーターの音)</t>
@@ -390,6 +387,42 @@
   <si>
     <t>ああああ</t>
   </si>
+  <si>
+    <r>
+      <t>doll,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ぬいぐるみ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>よくできたぬいぐるみだ</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -398,7 +431,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -417,6 +450,20 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -454,11 +501,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -716,19 +764,19 @@
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="G2" s="2"/>
       <c r="I2" s="2"/>
@@ -740,13 +788,13 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3"/>
@@ -766,8 +814,8 @@
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
+      <c r="D4" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -780,10 +828,10 @@
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="3"/>
@@ -798,10 +846,10 @@
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
@@ -816,10 +864,10 @@
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
@@ -834,10 +882,10 @@
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
@@ -852,13 +900,13 @@
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2"/>
       <c r="G9" s="2"/>
@@ -871,10 +919,10 @@
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2"/>
       <c r="E10" s="2"/>
@@ -888,16 +936,16 @@
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="E11" s="2"/>
       <c r="G11" s="2"/>
@@ -910,16 +958,16 @@
     </row>
     <row r="12" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2"/>
       <c r="G12" s="2"/>
@@ -932,16 +980,16 @@
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2"/>
       <c r="G13" s="2"/>
@@ -954,16 +1002,16 @@
     </row>
     <row r="14" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2"/>
       <c r="G14" s="2"/>
@@ -976,16 +1024,16 @@
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2"/>
       <c r="G15" s="2"/>
@@ -998,16 +1046,16 @@
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2"/>
       <c r="G16" s="2"/>
@@ -1020,16 +1068,16 @@
     </row>
     <row r="17" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2"/>
       <c r="G17" s="2"/>
@@ -1042,16 +1090,16 @@
     </row>
     <row r="18" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2"/>
       <c r="G18" s="2"/>
@@ -1064,16 +1112,16 @@
     </row>
     <row r="19" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2"/>
       <c r="G19" s="2"/>
@@ -1086,16 +1134,16 @@
     </row>
     <row r="20" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C20" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" s="2"/>
       <c r="G20" s="2"/>
@@ -1108,16 +1156,16 @@
     </row>
     <row r="21" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2"/>
       <c r="G21" s="2"/>
@@ -1130,16 +1178,16 @@
     </row>
     <row r="22" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="2"/>
       <c r="G22" s="2"/>
@@ -1152,16 +1200,16 @@
     </row>
     <row r="23" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2"/>
       <c r="G23" s="2"/>
@@ -1174,16 +1222,16 @@
     </row>
     <row r="24" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2"/>
       <c r="G24" s="2"/>
@@ -1196,16 +1244,16 @@
     </row>
     <row r="25" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" s="2"/>
       <c r="G25" s="2"/>
@@ -1218,16 +1266,16 @@
     </row>
     <row r="26" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2"/>
       <c r="G26" s="2"/>
@@ -1240,16 +1288,16 @@
     </row>
     <row r="27" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2"/>
       <c r="G27" s="2"/>
@@ -1262,16 +1310,16 @@
     </row>
     <row r="28" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2"/>
       <c r="G28" s="2"/>
@@ -1284,16 +1332,16 @@
     </row>
     <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2"/>
       <c r="G29" s="2"/>
@@ -1306,16 +1354,16 @@
     </row>
     <row r="30" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2"/>
       <c r="G30" s="2"/>
@@ -1328,16 +1376,16 @@
     </row>
     <row r="31" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2"/>
       <c r="G31" s="2"/>
@@ -1350,16 +1398,16 @@
     </row>
     <row r="32" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2"/>
       <c r="G32" s="2"/>
@@ -1372,16 +1420,16 @@
     </row>
     <row r="33" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" s="2"/>
       <c r="G33" s="2"/>
@@ -1394,16 +1442,16 @@
     </row>
     <row r="34" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2"/>
       <c r="G34" s="2"/>
@@ -1416,16 +1464,16 @@
     </row>
     <row r="35" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E35" s="2"/>
       <c r="G35" s="2"/>
@@ -1438,16 +1486,16 @@
     </row>
     <row r="36" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E36" s="2"/>
       <c r="G36" s="2"/>
@@ -1460,16 +1508,16 @@
     </row>
     <row r="37" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E37" s="2"/>
       <c r="G37" s="2"/>
@@ -1482,16 +1530,16 @@
     </row>
     <row r="38" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2"/>
       <c r="G38" s="2"/>
@@ -1504,16 +1552,16 @@
     </row>
     <row r="39" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E39" s="2"/>
       <c r="G39" s="2"/>
@@ -1526,16 +1574,16 @@
     </row>
     <row r="40" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E40" s="2"/>
       <c r="G40" s="2"/>
@@ -1548,16 +1596,16 @@
     </row>
     <row r="41" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E41" s="2"/>
       <c r="G41" s="2"/>
@@ -1570,16 +1618,16 @@
     </row>
     <row r="42" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" s="2"/>
       <c r="G42" s="2"/>
@@ -1592,16 +1640,16 @@
     </row>
     <row r="43" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E43" s="2"/>
       <c r="G43" s="2"/>
@@ -1614,16 +1662,16 @@
     </row>
     <row r="44" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44" s="2"/>
       <c r="G44" s="2"/>
@@ -1636,16 +1684,16 @@
     </row>
     <row r="45" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2"/>
       <c r="G45" s="2"/>
@@ -1658,16 +1706,16 @@
     </row>
     <row r="46" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" s="2"/>
       <c r="G46" s="2"/>
@@ -1680,16 +1728,16 @@
     </row>
     <row r="47" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E47" s="2"/>
       <c r="G47" s="2"/>
@@ -1702,16 +1750,16 @@
     </row>
     <row r="48" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48" s="2"/>
       <c r="G48" s="2"/>
@@ -1724,16 +1772,16 @@
     </row>
     <row r="49" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E49" s="2"/>
       <c r="G49" s="2"/>
@@ -1746,16 +1794,16 @@
     </row>
     <row r="50" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2"/>
       <c r="G50" s="2"/>
@@ -1768,16 +1816,16 @@
     </row>
     <row r="51" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E51" s="2"/>
       <c r="G51" s="2"/>
@@ -1790,16 +1838,16 @@
     </row>
     <row r="52" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52" s="2"/>
       <c r="G52" s="2"/>
@@ -1812,16 +1860,16 @@
     </row>
     <row r="53" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E53" s="2"/>
       <c r="G53" s="2"/>
@@ -1834,16 +1882,16 @@
     </row>
     <row r="54" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E54" s="2"/>
       <c r="G54" s="2"/>
@@ -1856,16 +1904,16 @@
     </row>
     <row r="55" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E55" s="2"/>
       <c r="G55" s="2"/>
@@ -1878,16 +1926,16 @@
     </row>
     <row r="56" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E56" s="2"/>
       <c r="G56" s="2"/>
@@ -1900,16 +1948,16 @@
     </row>
     <row r="57" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2"/>
       <c r="G57" s="2"/>
@@ -1922,16 +1970,16 @@
     </row>
     <row r="58" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E58" s="2"/>
       <c r="G58" s="2"/>
@@ -1944,16 +1992,16 @@
     </row>
     <row r="59" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E59" s="2"/>
       <c r="G59" s="2"/>
@@ -1966,16 +2014,16 @@
     </row>
     <row r="60" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E60" s="2"/>
       <c r="G60" s="2"/>
@@ -1988,16 +2036,16 @@
     </row>
     <row r="61" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" s="2"/>
       <c r="G61" s="2"/>
@@ -2010,16 +2058,16 @@
     </row>
     <row r="62" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E62" s="2"/>
       <c r="G62" s="2"/>
@@ -2032,22 +2080,22 @@
     </row>
     <row r="63" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G63" s="2"/>
       <c r="I63" s="2"/>
@@ -2059,16 +2107,16 @@
     </row>
     <row r="64" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E64" s="2"/>
       <c r="G64" s="2"/>
@@ -2081,16 +2129,16 @@
     </row>
     <row r="65" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E65" s="2"/>
       <c r="G65" s="2"/>
@@ -2103,16 +2151,16 @@
     </row>
     <row r="66" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E66" s="2"/>
       <c r="G66" s="2"/>
@@ -2125,16 +2173,16 @@
     </row>
     <row r="67" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67" s="2"/>
       <c r="G67" s="2"/>
@@ -2147,16 +2195,16 @@
     </row>
     <row r="68" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E68" s="2"/>
       <c r="G68" s="2"/>
@@ -2169,16 +2217,16 @@
     </row>
     <row r="69" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E69" s="2"/>
       <c r="G69" s="2"/>
@@ -2191,16 +2239,16 @@
     </row>
     <row r="70" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E70" s="2"/>
       <c r="G70" s="2"/>
@@ -2213,16 +2261,16 @@
     </row>
     <row r="71" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E71" s="2"/>
       <c r="G71" s="2"/>
@@ -2235,7 +2283,7 @@
     </row>
     <row r="72" spans="1:19" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C72" s="2"/>
       <c r="E72" s="2"/>
@@ -12520,10 +12568,10 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2"/>
       <c r="E2" s="2"/>
@@ -23569,16 +23617,16 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="3"/>
@@ -23592,10 +23640,10 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="3"/>
@@ -23610,10 +23658,10 @@
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3"/>
@@ -34640,28 +34688,28 @@
     </row>
     <row r="2" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" s="2">
         <v>0.2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F2" s="3">
         <v>45658</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I2" s="2"/>
       <c r="K2" s="2"/>
@@ -34672,13 +34720,13 @@
     </row>
     <row r="3" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>5</v>
@@ -34694,16 +34742,16 @@
     </row>
     <row r="4" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="2"/>
@@ -34716,13 +34764,13 @@
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="D5" s="2">
         <v>0.5</v>
@@ -34738,16 +34786,16 @@
     </row>
     <row r="6" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2"/>
       <c r="G6" s="2"/>
@@ -34760,16 +34808,16 @@
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E7" s="2"/>
       <c r="G7" s="2"/>
@@ -34782,10 +34830,10 @@
     </row>
     <row r="8" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -12431,7 +12431,7 @@
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G61 C2:C1000 E2:E1000 G63:G1000 I2:I1000 K2:K1000 M2:M1000 O2:O1000 Q2:Q1000 S2:S1000">
-      <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName,GetItem"</formula1>
+      <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName,GetItem,Choice"</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId1"/>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="206">
   <si>
     <t>SpeakerName</t>
   </si>
@@ -72,34 +72,7 @@
     <t>………。ん……。</t>
   </si>
   <si>
-    <t>あ</t>
-  </si>
-  <si>
-    <t>CardChoice</t>
-  </si>
-  <si>
-    <t>[光の札を選ぶ,光の札]/[影の札を選ぶ,影の札]</t>
-  </si>
-  <si>
-    <t>選択</t>
-  </si>
-  <si>
-    <t>Choice</t>
-  </si>
-  <si>
-    <t>どれ？,A,B</t>
-  </si>
-  <si>
     <t>あれ……ここは……？</t>
-  </si>
-  <si>
-    <t>カード獲得</t>
-  </si>
-  <si>
-    <t>GetCard</t>
-  </si>
-  <si>
-    <t>ture</t>
   </si>
   <si>
     <t>………………。</t>
@@ -318,7 +291,7 @@
     <t>GetItem</t>
   </si>
   <si>
-    <t>Card,精神札,精神札だ。</t>
+    <t xml:space="preserve">Card,精神札, </t>
   </si>
   <si>
     <t>あなたの"価値"を数値化したものです。</t>
@@ -420,6 +393,12 @@
     <t>指先が、ゆっくりと動く。</t>
   </si>
   <si>
+    <t>CardChoice</t>
+  </si>
+  <si>
+    <t>[光の札を選ぶ,LightCard]/[影の札を選ぶ,ShadowCard]</t>
+  </si>
+  <si>
     <t>（カタン、と小さな音がして、エレベーターが登り始めた）</t>
   </si>
   <si>
@@ -462,9 +441,13 @@
     <t>「もしかして……同じ札を選んだ人と、マッチングされるのかな」</t>
   </si>
   <si>
-    <t>「おそらく、そうね。 私たちは、あの仮面の支配人から提示された二択で、
-同じものを選んでここに来た。 
-似たような感性の持ち主と、戦わせられるってことなのかも」</t>
+    <t xml:space="preserve">「おそらく、そうね。 
+私たちは、あの仮面の支配人から提示された二択で、
+同じものを選んでここに来た。 」
+</t>
+  </si>
+  <si>
+    <t>「似たような感性の持ち主と、戦わせられるってことなのかも」</t>
   </si>
   <si>
     <t>「……記憶は失われてるのに、心の奥底に染みついた考え方は変わらないって感じがする。」</t>
@@ -567,8 +550,10 @@
   </si>
   <si>
     <t>「自分の“本当の記憶”なんて、私たちに判別する方法は最初から存在しないの。 
-でもね、ここで落札した記憶は、すべて“自分の記憶”になる。 
-本来の持ち主が誰だろうと、関係ないわ」</t>
+でもね、ここで落札した記憶は、すべて“自分の記憶”になる。 」</t>
+  </si>
+  <si>
+    <t>「本来の持ち主が誰だろうと、関係ないわ」</t>
   </si>
   <si>
     <t>「……それって……」</t>
@@ -578,7 +563,8 @@
   </si>
   <si>
     <t>「じゃあ私は……何のためにこのオークションに参加したの？ 
-私は、自分を取り戻したいのに……それがもう出来ないなんて、聞いてない……！」</t>
+私は、自分を取り戻したいのに……
+それがもう出来ないなんて、聞いてない……！」</t>
   </si>
   <si>
     <t>「私に……もう参加する理由なんて……！」</t>
@@ -614,22 +600,23 @@
 私の感情で、私の記憶を落札してみせる」</t>
   </si>
   <si>
-    <t>システム</t>
-  </si>
-  <si>
-    <t>アルファ版はここまでです。</t>
+    <t>ベータ版はここまでです。</t>
   </si>
   <si>
     <t>プレイしていただきありがとうございます。</t>
   </si>
   <si>
-    <t>製品版リリースをお待ちください。</t>
+    <t>ゲームを気に入っていただけたら、
+Steamでのウィッシュリスト登録をお願いします。</t>
   </si>
   <si>
     <t>速度0.2のセリフ</t>
   </si>
   <si>
     <t>CustomCharSpeed</t>
+  </si>
+  <si>
+    <t>システム</t>
   </si>
   <si>
     <t>速度5のセリフ</t>
@@ -1054,7 +1041,6 @@
         <v>17</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="4"/>
       <c r="E4" s="3"/>
       <c r="G4" s="3"/>
       <c r="I4" s="3"/>
@@ -1065,16 +1051,14 @@
       <c r="S4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="3"/>
@@ -1085,16 +1069,14 @@
       <c r="S5" s="3"/>
     </row>
     <row r="6">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B6" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="3"/>
       <c r="G6" s="3"/>
       <c r="I6" s="3"/>
@@ -1109,7 +1091,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="4"/>
@@ -1123,15 +1105,14 @@
       <c r="S7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E8" s="3"/>
       <c r="G8" s="3"/>
@@ -1147,10 +1128,9 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
       <c r="E9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="3"/>
@@ -1162,13 +1142,17 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="C10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E10" s="3"/>
       <c r="G10" s="3"/>
       <c r="I10" s="3"/>
@@ -1179,14 +1163,17 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3"/>
       <c r="G11" s="3"/>
@@ -1202,9 +1189,14 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
@@ -1216,16 +1208,16 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3"/>
       <c r="G13" s="3"/>
@@ -1238,16 +1230,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3"/>
       <c r="G14" s="3"/>
@@ -1263,13 +1255,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3"/>
       <c r="G15" s="3"/>
@@ -1282,16 +1274,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
@@ -1304,13 +1296,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>36</v>
@@ -1326,16 +1318,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3"/>
       <c r="G18" s="3"/>
@@ -1348,16 +1340,16 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
@@ -1370,16 +1362,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E20" s="3"/>
       <c r="G20" s="3"/>
@@ -1392,16 +1384,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E21" s="3"/>
       <c r="G21" s="3"/>
@@ -1414,16 +1406,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E22" s="3"/>
       <c r="G22" s="3"/>
@@ -1436,16 +1428,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E23" s="3"/>
       <c r="G23" s="3"/>
@@ -1458,16 +1450,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24" s="3"/>
       <c r="G24" s="3"/>
@@ -1480,16 +1472,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3"/>
       <c r="G25" s="3"/>
@@ -1502,16 +1494,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E26" s="3"/>
       <c r="G26" s="3"/>
@@ -1524,16 +1516,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E27" s="3"/>
       <c r="G27" s="3"/>
@@ -1546,16 +1538,16 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E28" s="3"/>
       <c r="G28" s="3"/>
@@ -1568,16 +1560,16 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E29" s="3"/>
       <c r="G29" s="3"/>
@@ -1590,16 +1582,16 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E30" s="3"/>
       <c r="G30" s="3"/>
@@ -1612,16 +1604,16 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E31" s="3"/>
       <c r="G31" s="3"/>
@@ -1637,13 +1629,13 @@
         <v>16</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E32" s="3"/>
       <c r="G32" s="3"/>
@@ -1656,16 +1648,16 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E33" s="3"/>
       <c r="G33" s="3"/>
@@ -1678,16 +1670,16 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3"/>
       <c r="G34" s="3"/>
@@ -1700,16 +1692,16 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="E35" s="3"/>
       <c r="G35" s="3"/>
@@ -1722,16 +1714,16 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E36" s="3"/>
       <c r="G36" s="3"/>
@@ -1744,16 +1736,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="E37" s="3"/>
       <c r="G37" s="3"/>
@@ -1766,16 +1758,16 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E38" s="3"/>
       <c r="G38" s="3"/>
@@ -1791,13 +1783,13 @@
         <v>16</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E39" s="3"/>
       <c r="G39" s="3"/>
@@ -1810,16 +1802,16 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E40" s="3"/>
       <c r="G40" s="3"/>
@@ -1832,16 +1824,16 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E41" s="3"/>
       <c r="G41" s="3"/>
@@ -1854,16 +1846,16 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E42" s="3"/>
       <c r="G42" s="3"/>
@@ -1876,16 +1868,16 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E43" s="3"/>
       <c r="G43" s="3"/>
@@ -1898,16 +1890,16 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E44" s="3"/>
       <c r="G44" s="3"/>
@@ -1920,16 +1912,16 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="E45" s="3"/>
       <c r="G45" s="3"/>
@@ -1942,16 +1934,16 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E46" s="3"/>
       <c r="G46" s="3"/>
@@ -1967,13 +1959,13 @@
         <v>16</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E47" s="3"/>
       <c r="G47" s="3"/>
@@ -1986,16 +1978,16 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E48" s="3"/>
       <c r="G48" s="3"/>
@@ -2008,16 +2000,16 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E49" s="3"/>
       <c r="G49" s="3"/>
@@ -2030,16 +2022,16 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="E50" s="3"/>
       <c r="G50" s="3"/>
@@ -2052,16 +2044,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="E51" s="3"/>
       <c r="G51" s="3"/>
@@ -2074,16 +2066,16 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="E52" s="3"/>
       <c r="G52" s="3"/>
@@ -2096,16 +2088,16 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E53" s="3"/>
       <c r="G53" s="3"/>
@@ -2118,16 +2110,16 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E54" s="3"/>
       <c r="G54" s="3"/>
@@ -2140,16 +2132,16 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E55" s="3"/>
       <c r="G55" s="3"/>
@@ -2162,16 +2154,16 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E56" s="3"/>
       <c r="G56" s="3"/>
@@ -2184,16 +2176,16 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E57" s="3"/>
       <c r="G57" s="3"/>
@@ -2206,16 +2198,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E58" s="3"/>
       <c r="G58" s="3"/>
@@ -2228,16 +2220,16 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E59" s="3"/>
       <c r="G59" s="3"/>
@@ -2250,16 +2242,16 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E60" s="3"/>
       <c r="G60" s="3"/>
@@ -2272,16 +2264,16 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E61" s="3"/>
       <c r="G61" s="3"/>
@@ -2294,19 +2286,23 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
-      <c r="E62" s="3"/>
-      <c r="G62" s="3"/>
+      <c r="E62" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="I62" s="3"/>
       <c r="K62" s="3"/>
       <c r="M62" s="3"/>
@@ -2316,16 +2312,16 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E63" s="3"/>
       <c r="G63" s="3"/>
@@ -2338,16 +2334,16 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E64" s="3"/>
       <c r="G64" s="3"/>
@@ -2360,23 +2356,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>100</v>
-      </c>
+      <c r="E65" s="3"/>
+      <c r="G65" s="3"/>
       <c r="I65" s="3"/>
       <c r="K65" s="3"/>
       <c r="M65" s="3"/>
@@ -2386,16 +2378,16 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E66" s="3"/>
       <c r="G66" s="3"/>
@@ -2408,16 +2400,16 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E67" s="3"/>
       <c r="G67" s="3"/>
@@ -2430,16 +2422,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
@@ -2452,16 +2444,16 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E69" s="3"/>
       <c r="G69" s="3"/>
@@ -2474,13 +2466,13 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>51</v>
@@ -2495,18 +2487,10 @@
       <c r="S70" s="3"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="s">
-        <v>47</v>
+      <c r="B71" s="2" t="s">
+        <v>100</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>36</v>
-      </c>
+      <c r="C71" s="3"/>
       <c r="E71" s="3"/>
       <c r="G71" s="3"/>
       <c r="I71" s="3"/>
@@ -2517,18 +2501,7 @@
       <c r="S71" s="3"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="C72" s="3"/>
       <c r="E72" s="3"/>
       <c r="G72" s="3"/>
       <c r="I72" s="3"/>
@@ -2539,18 +2512,7 @@
       <c r="S72" s="3"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="C73" s="3"/>
       <c r="E73" s="3"/>
       <c r="G73" s="3"/>
       <c r="I73" s="3"/>
@@ -2561,9 +2523,6 @@
       <c r="S73" s="3"/>
     </row>
     <row r="74">
-      <c r="B74" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="C74" s="3"/>
       <c r="E74" s="3"/>
       <c r="G74" s="3"/>
@@ -12760,42 +12719,9 @@
       <c r="Q1000" s="3"/>
       <c r="S1000" s="3"/>
     </row>
-    <row r="1001">
-      <c r="C1001" s="3"/>
-      <c r="E1001" s="3"/>
-      <c r="G1001" s="3"/>
-      <c r="I1001" s="3"/>
-      <c r="K1001" s="3"/>
-      <c r="M1001" s="3"/>
-      <c r="O1001" s="3"/>
-      <c r="Q1001" s="3"/>
-      <c r="S1001" s="3"/>
-    </row>
-    <row r="1002">
-      <c r="C1002" s="3"/>
-      <c r="E1002" s="3"/>
-      <c r="G1002" s="3"/>
-      <c r="I1002" s="3"/>
-      <c r="K1002" s="3"/>
-      <c r="M1002" s="3"/>
-      <c r="O1002" s="3"/>
-      <c r="Q1002" s="3"/>
-      <c r="S1002" s="3"/>
-    </row>
-    <row r="1003">
-      <c r="C1003" s="3"/>
-      <c r="E1003" s="3"/>
-      <c r="G1003" s="3"/>
-      <c r="I1003" s="3"/>
-      <c r="K1003" s="3"/>
-      <c r="M1003" s="3"/>
-      <c r="O1003" s="3"/>
-      <c r="Q1003" s="3"/>
-      <c r="S1003" s="3"/>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G64 C2:C1003 E2:E1003 G66:G1003 I2:I1003 K2:K1003 M2:M1003 O2:O1003 Q2:Q1003 S2:S1003">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G61 C2:C1000 E2:E1000 G63:G1000 I2:I1000 K2:K1000 M2:M1000 O2:O1000 Q2:Q1000 S2:S1000">
       <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName,GetItem,Choice,GetCard,CardChoice"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12846,7 +12772,7 @@
     <row r="2">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
@@ -12866,7 +12792,7 @@
     <row r="3">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C3" s="3"/>
       <c r="E3" s="2"/>
@@ -12882,7 +12808,7 @@
     <row r="4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="4"/>
@@ -12898,7 +12824,7 @@
     <row r="5">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C5" s="3"/>
       <c r="E5" s="3"/>
@@ -12912,16 +12838,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3"/>
       <c r="G6" s="3"/>
@@ -12934,16 +12860,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E7" s="3"/>
       <c r="G7" s="3"/>
@@ -12956,16 +12882,16 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3"/>
       <c r="G8" s="3"/>
@@ -12978,16 +12904,16 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3"/>
       <c r="G9" s="3"/>
@@ -13000,16 +12926,16 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E10" s="3"/>
       <c r="G10" s="3"/>
@@ -13022,16 +12948,16 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3"/>
       <c r="G11" s="3"/>
@@ -13045,13 +12971,13 @@
     <row r="12">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E12" s="3"/>
       <c r="G12" s="3"/>
@@ -13064,16 +12990,16 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E13" s="3"/>
       <c r="G13" s="3"/>
@@ -13089,13 +13015,13 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E14" s="3"/>
       <c r="G14" s="3"/>
@@ -13108,16 +13034,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E15" s="3"/>
       <c r="G15" s="3"/>
@@ -13130,16 +13056,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
@@ -13153,13 +13079,13 @@
     <row r="17">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3"/>
       <c r="G17" s="3"/>
@@ -13173,13 +13099,13 @@
     <row r="18">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3"/>
       <c r="G18" s="3"/>
@@ -13193,13 +13119,13 @@
     <row r="19">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
@@ -13212,16 +13138,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E20" s="3"/>
       <c r="G20" s="3"/>
@@ -13234,16 +13160,16 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="E21" s="3"/>
       <c r="G21" s="3"/>
@@ -13256,16 +13182,16 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E22" s="3"/>
       <c r="G22" s="3"/>
@@ -13279,13 +13205,13 @@
     <row r="23">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E23" s="3"/>
       <c r="G23" s="3"/>
@@ -13299,13 +13225,13 @@
     <row r="24">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>20</v>
+        <v>126</v>
       </c>
       <c r="E24" s="3"/>
       <c r="G24" s="3"/>
@@ -24206,13 +24132,13 @@
     </row>
     <row r="2">
       <c r="B2" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="4"/>
@@ -24226,7 +24152,7 @@
     </row>
     <row r="3">
       <c r="B3" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C3" s="2"/>
       <c r="E3" s="3"/>
@@ -24240,7 +24166,7 @@
     </row>
     <row r="4">
       <c r="B4" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C4" s="2"/>
       <c r="E4" s="3"/>
@@ -24254,7 +24180,7 @@
     </row>
     <row r="5">
       <c r="B5" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C5" s="2"/>
       <c r="E5" s="3"/>
@@ -24268,13 +24194,13 @@
     </row>
     <row r="6">
       <c r="B6" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3"/>
       <c r="G6" s="3"/>
@@ -24287,16 +24213,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E7" s="3"/>
       <c r="G7" s="3"/>
@@ -24309,13 +24235,13 @@
     </row>
     <row r="8">
       <c r="B8" s="2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E8" s="3"/>
       <c r="G8" s="3"/>
@@ -24328,13 +24254,13 @@
     </row>
     <row r="9">
       <c r="B9" s="2" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E9" s="3"/>
       <c r="G9" s="3"/>
@@ -24350,13 +24276,13 @@
         <v>16</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E10" s="3"/>
       <c r="G10" s="3"/>
@@ -24369,16 +24295,16 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E11" s="3"/>
       <c r="G11" s="3"/>
@@ -24394,13 +24320,13 @@
         <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E12" s="3"/>
       <c r="G12" s="3"/>
@@ -24413,16 +24339,16 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E13" s="3"/>
       <c r="G13" s="3"/>
@@ -24435,16 +24361,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E14" s="3"/>
       <c r="G14" s="3"/>
@@ -24457,16 +24383,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E15" s="3"/>
       <c r="G15" s="3"/>
@@ -24478,14 +24404,17 @@
       <c r="S15" s="3"/>
     </row>
     <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B16" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
@@ -24497,17 +24426,14 @@
       <c r="S16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E17" s="3"/>
       <c r="G17" s="3"/>
@@ -24520,16 +24446,16 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3"/>
       <c r="G18" s="3"/>
@@ -24542,16 +24468,16 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E19" s="3"/>
       <c r="G19" s="3"/>
@@ -24564,16 +24490,16 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E20" s="3"/>
       <c r="G20" s="3"/>
@@ -24585,14 +24511,17 @@
       <c r="S20" s="3"/>
     </row>
     <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E21" s="3"/>
       <c r="G21" s="3"/>
@@ -24604,17 +24533,14 @@
       <c r="S21" s="3"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="B22" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="E22" s="3"/>
       <c r="G22" s="3"/>
@@ -24627,16 +24553,16 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E23" s="3"/>
       <c r="G23" s="3"/>
@@ -24649,16 +24575,16 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E24" s="3"/>
       <c r="G24" s="3"/>
@@ -24670,14 +24596,17 @@
       <c r="S24" s="3"/>
     </row>
     <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B25" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E25" s="3"/>
       <c r="G25" s="3"/>
@@ -24690,13 +24619,13 @@
     </row>
     <row r="26">
       <c r="B26" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E26" s="3"/>
       <c r="G26" s="3"/>
@@ -24708,17 +24637,14 @@
       <c r="S26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="B27" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E27" s="3"/>
       <c r="G27" s="3"/>
@@ -24730,10 +24656,18 @@
       <c r="S27" s="3"/>
     </row>
     <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B28" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>149</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="G28" s="3"/>
       <c r="I28" s="3"/>
@@ -24744,6 +24678,9 @@
       <c r="S28" s="3"/>
     </row>
     <row r="29">
+      <c r="B29" s="2" t="s">
+        <v>159</v>
+      </c>
       <c r="C29" s="3"/>
       <c r="E29" s="3"/>
       <c r="G29" s="3"/>
@@ -35435,9 +35372,20 @@
       <c r="Q1000" s="3"/>
       <c r="S1000" s="3"/>
     </row>
+    <row r="1001">
+      <c r="C1001" s="3"/>
+      <c r="E1001" s="3"/>
+      <c r="G1001" s="3"/>
+      <c r="I1001" s="3"/>
+      <c r="K1001" s="3"/>
+      <c r="M1001" s="3"/>
+      <c r="O1001" s="3"/>
+      <c r="Q1001" s="3"/>
+      <c r="S1001" s="3"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C5 C7:C1000 E2:E1000 G2:G1000 I2:I1000 K2:K1000 M2:M1000 O2:O1000 Q2:Q1000 S2:S1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C5 C7:C1001 E2:E1001 G2:G1001 I2:I1001 K2:K1001 M2:M1001 O2:O1001 Q2:Q1001 S2:S1001">
       <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2 C6">
@@ -35455,7 +35403,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="71.13"/>
+    <col customWidth="1" min="2" max="2" width="69.38"/>
     <col customWidth="1" min="3" max="7" width="15.38"/>
   </cols>
   <sheetData>
@@ -35490,7 +35438,7 @@
     </row>
     <row r="2">
       <c r="B2" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
@@ -35513,7 +35461,7 @@
         <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C3" s="2"/>
       <c r="E3" s="3"/>
@@ -35527,16 +35475,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E4" s="3"/>
       <c r="G4" s="3"/>
@@ -35549,7 +35497,7 @@
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C5" s="2"/>
       <c r="E5" s="3"/>
@@ -35563,7 +35511,7 @@
     </row>
     <row r="6">
       <c r="B6" s="5" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C6" s="2"/>
       <c r="E6" s="3"/>
@@ -35577,7 +35525,7 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="3"/>
@@ -35591,7 +35539,7 @@
     </row>
     <row r="8">
       <c r="B8" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -35606,7 +35554,7 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C9" s="3"/>
       <c r="E9" s="3"/>
@@ -35620,7 +35568,7 @@
     </row>
     <row r="10">
       <c r="B10" s="5" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C10" s="3"/>
       <c r="E10" s="3"/>
@@ -35634,7 +35582,7 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C11" s="3"/>
       <c r="E11" s="3"/>
@@ -35648,7 +35596,7 @@
     </row>
     <row r="12">
       <c r="B12" s="5" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C12" s="3"/>
       <c r="E12" s="3"/>
@@ -35665,7 +35613,7 @@
         <v>16</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C13" s="3"/>
       <c r="E13" s="3"/>
@@ -35679,16 +35627,16 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E14" s="3"/>
       <c r="G14" s="3"/>
@@ -35704,13 +35652,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E15" s="3"/>
       <c r="G15" s="3"/>
@@ -35723,16 +35671,16 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
@@ -35745,12 +35693,17 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>147</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
@@ -35761,8 +35714,11 @@
       <c r="S17" s="3"/>
     </row>
     <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="B18" s="5" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C18" s="3"/>
       <c r="E18" s="3"/>
@@ -35775,11 +35731,8 @@
       <c r="S18" s="3"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="B19" s="5" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C19" s="3"/>
       <c r="E19" s="3"/>
@@ -35796,7 +35749,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C20" s="3"/>
       <c r="E20" s="3"/>
@@ -35809,8 +35762,11 @@
       <c r="S20" s="3"/>
     </row>
     <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B21" s="5" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C21" s="3"/>
       <c r="E21" s="3"/>
@@ -35823,18 +35779,10 @@
       <c r="S21" s="3"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="s">
-        <v>153</v>
+      <c r="B22" s="5" t="s">
+        <v>180</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="C22" s="3"/>
       <c r="E22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
@@ -35845,14 +35793,17 @@
       <c r="S22" s="3"/>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="s">
-        <v>186</v>
+      <c r="A23" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E23" s="3"/>
       <c r="G23" s="3"/>
@@ -35864,17 +35815,14 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="B24" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E24" s="3"/>
       <c r="G24" s="3"/>
@@ -35887,16 +35835,16 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E25" s="3"/>
       <c r="G25" s="3"/>
@@ -35909,16 +35857,16 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E26" s="3"/>
       <c r="G26" s="3"/>
@@ -35931,16 +35879,16 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E27" s="3"/>
       <c r="G27" s="3"/>
@@ -35952,10 +35900,18 @@
       <c r="S27" s="3"/>
     </row>
     <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B28" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
-      <c r="C28" s="3"/>
+      <c r="C28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="E28" s="3"/>
       <c r="G28" s="3"/>
       <c r="I28" s="3"/>
@@ -35967,7 +35923,7 @@
     </row>
     <row r="29">
       <c r="B29" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C29" s="3"/>
       <c r="E29" s="3"/>
@@ -35980,11 +35936,8 @@
       <c r="S29" s="3"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="B30" s="5" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C30" s="3"/>
       <c r="E30" s="3"/>
@@ -35997,6 +35950,12 @@
       <c r="S30" s="3"/>
     </row>
     <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>188</v>
+      </c>
       <c r="C31" s="3"/>
       <c r="E31" s="3"/>
       <c r="G31" s="3"/>
@@ -46655,9 +46614,20 @@
       <c r="Q999" s="3"/>
       <c r="S999" s="3"/>
     </row>
+    <row r="1000">
+      <c r="C1000" s="3"/>
+      <c r="E1000" s="3"/>
+      <c r="G1000" s="3"/>
+      <c r="I1000" s="3"/>
+      <c r="K1000" s="3"/>
+      <c r="M1000" s="3"/>
+      <c r="O1000" s="3"/>
+      <c r="Q1000" s="3"/>
+      <c r="S1000" s="3"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C999 E2:E999 G2:G999 I2:I999 K2:K999 M2:M999 O2:O999 Q2:Q999 S2:S999">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C1000 E2:E1000 G2:G1000 I2:I1000 K2:K1000 M2:M1000 O2:O1000 Q2:Q1000 S2:S1000">
       <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2">
@@ -46709,17 +46679,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="B2" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="4"/>
@@ -46732,11 +46699,8 @@
       <c r="S2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="B3" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="4"/>
@@ -46750,11 +46714,8 @@
       <c r="S3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>194</v>
-      </c>
       <c r="B4" s="2" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="4"/>
@@ -57779,19 +57740,19 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D2" s="2">
         <v>0.2</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F2" s="4">
         <v>45658.0</v>
@@ -57800,7 +57761,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I2" s="3"/>
       <c r="K2" s="3"/>
@@ -57814,10 +57775,10 @@
         <v>194</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D3" s="2">
         <v>5.0</v>
@@ -57833,16 +57794,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E4" s="3"/>
       <c r="G4" s="3"/>
@@ -57855,13 +57816,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2">
         <v>0.5</v>
@@ -57877,10 +57838,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
@@ -57899,16 +57860,16 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E7" s="3"/>
       <c r="G7" s="3"/>
@@ -57921,10 +57882,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>

--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="204">
   <si>
     <t>SpeakerName</t>
   </si>
@@ -507,7 +507,7 @@
 この先に、何が待っているんだろう）</t>
   </si>
   <si>
-    <t>（空間が変わる。私とセリカの前に、五枚の札が浮かび上がる）</t>
+    <t>（空間が変わる。私とセリカの前に、三枚の札が浮かび上がる）</t>
   </si>
   <si>
     <t>「これが……商品？」</t>
@@ -522,16 +522,10 @@
     <t>壊れた約束：交わされた約束は果たされず、信頼が静かに失われた。</t>
   </si>
   <si>
-    <t>赦せなかった手紙：届かなかった謝罪の手紙。封を切らなかった理由は不明。</t>
+    <t>信じた罰：何もかも信じていた自分が、一番の愚か者だったと気づかされた。</t>
   </si>
   <si>
-    <t>笑顔の仮面：貼りつけられた笑顔の裏で、誰にも本音を見せなかった人物の記憶。</t>
-  </si>
-  <si>
-    <t>赤い傘の記憶：雨の日に交わされた言葉。傘はもう存在しない。</t>
-  </si>
-  <si>
-    <t>怒りの種：些細な言葉が心に傷を残し、怒りへと育った記憶。</t>
+    <t>触れてしまった温度：壊したかったはずの存在が、気づけば温もりとして胸に残っていた。</t>
   </si>
   <si>
     <t>（それぞれの札が、機械のような声で説明されていく）</t>
@@ -35581,6 +35575,9 @@
       <c r="S10" s="3"/>
     </row>
     <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B11" s="5" t="s">
         <v>169</v>
       </c>
@@ -35595,10 +35592,18 @@
       <c r="S11" s="3"/>
     </row>
     <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B12" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E12" s="3"/>
       <c r="G12" s="3"/>
       <c r="I12" s="3"/>
@@ -35615,7 +35620,12 @@
       <c r="B13" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E13" s="3"/>
       <c r="G13" s="3"/>
       <c r="I13" s="3"/>
@@ -35649,7 +35659,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>173</v>
@@ -35671,17 +35681,12 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="C16" s="3"/>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
       <c r="I16" s="3"/>
@@ -35692,18 +35697,10 @@
       <c r="S16" s="3"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="B17" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="C17" s="3"/>
       <c r="E17" s="3"/>
       <c r="G17" s="3"/>
       <c r="I17" s="3"/>
@@ -35715,7 +35712,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>176</v>
@@ -35731,6 +35728,9 @@
       <c r="S18" s="3"/>
     </row>
     <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B19" s="5" t="s">
         <v>177</v>
       </c>
@@ -35745,9 +35745,6 @@
       <c r="S19" s="3"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="B20" s="5" t="s">
         <v>178</v>
       </c>
@@ -35763,12 +35760,17 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>16</v>
+        <v>147</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>179</v>
+      <c r="B21" s="2" t="s">
+        <v>154</v>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>139</v>
+      </c>
       <c r="E21" s="3"/>
       <c r="G21" s="3"/>
       <c r="I21" s="3"/>
@@ -35780,9 +35782,14 @@
     </row>
     <row r="22">
       <c r="B22" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="E22" s="3"/>
       <c r="G22" s="3"/>
       <c r="I22" s="3"/>
@@ -35796,14 +35803,14 @@
       <c r="A23" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>154</v>
+      <c r="B23" s="5" t="s">
+        <v>180</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E23" s="3"/>
       <c r="G23" s="3"/>
@@ -35815,6 +35822,9 @@
       <c r="S23" s="3"/>
     </row>
     <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="B24" s="5" t="s">
         <v>181</v>
       </c>
@@ -35878,18 +35888,10 @@
       <c r="S26" s="3"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="B27" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="C27" s="3"/>
       <c r="E27" s="3"/>
       <c r="G27" s="3"/>
       <c r="I27" s="3"/>
@@ -35900,18 +35902,10 @@
       <c r="S27" s="3"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="B28" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="C28" s="3"/>
       <c r="E28" s="3"/>
       <c r="G28" s="3"/>
       <c r="I28" s="3"/>
@@ -35922,6 +35916,9 @@
       <c r="S28" s="3"/>
     </row>
     <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="B29" s="5" t="s">
         <v>186</v>
       </c>
@@ -35936,9 +35933,6 @@
       <c r="S29" s="3"/>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="s">
-        <v>187</v>
-      </c>
       <c r="C30" s="3"/>
       <c r="E30" s="3"/>
       <c r="G30" s="3"/>
@@ -35950,12 +35944,6 @@
       <c r="S30" s="3"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>188</v>
-      </c>
       <c r="C31" s="3"/>
       <c r="E31" s="3"/>
       <c r="G31" s="3"/>
@@ -46603,31 +46591,9 @@
       <c r="Q998" s="3"/>
       <c r="S998" s="3"/>
     </row>
-    <row r="999">
-      <c r="C999" s="3"/>
-      <c r="E999" s="3"/>
-      <c r="G999" s="3"/>
-      <c r="I999" s="3"/>
-      <c r="K999" s="3"/>
-      <c r="M999" s="3"/>
-      <c r="O999" s="3"/>
-      <c r="Q999" s="3"/>
-      <c r="S999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="C1000" s="3"/>
-      <c r="E1000" s="3"/>
-      <c r="G1000" s="3"/>
-      <c r="I1000" s="3"/>
-      <c r="K1000" s="3"/>
-      <c r="M1000" s="3"/>
-      <c r="O1000" s="3"/>
-      <c r="Q1000" s="3"/>
-      <c r="S1000" s="3"/>
-    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C1000 E2:E1000 G2:G1000 I2:I1000 K2:K1000 M2:M1000 O2:O1000 Q2:Q1000 S2:S1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C3:C998 E2:E998 G2:G998 I2:I998 K2:K998 M2:M998 O2:O998 Q2:Q998 S2:S998">
       <formula1>"CharacterImageName,SEClipName,CustomCharSpeed,AutoAdvance,BackgroundImageName"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C2">
@@ -46680,7 +46646,7 @@
     </row>
     <row r="2">
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>12</v>
@@ -46700,7 +46666,7 @@
     </row>
     <row r="3">
       <c r="B3" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="4"/>
@@ -46715,7 +46681,7 @@
     </row>
     <row r="4">
       <c r="B4" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="4"/>
@@ -57743,10 +57709,10 @@
         <v>38</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D2" s="2">
         <v>0.2</v>
@@ -57772,13 +57738,13 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D3" s="2">
         <v>5.0</v>
@@ -57794,16 +57760,16 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E4" s="3"/>
       <c r="G4" s="3"/>
@@ -57816,13 +57782,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2">
         <v>0.5</v>
@@ -57838,10 +57804,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
@@ -57860,10 +57826,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>12</v>
@@ -57882,10 +57848,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
